--- a/data/实验一细胞培养板.xlsx
+++ b/data/实验一细胞培养板.xlsx
@@ -11,6 +11,18 @@
     <sheet name="细胞培养板2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="细胞培养板3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="细胞培养板4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="细胞培养板5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="细胞培养板6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="细胞培养板7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="细胞培养板8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="细胞培养板9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="细胞培养板10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="细胞培养板11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="细胞培养板12" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="细胞培养板13" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="细胞培养板14" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="细胞培养板15" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="细胞培养板16" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1047,6 +1059,4262 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板10ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板11ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板12ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板13ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板14ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板15ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板16ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2869,4 +7137,3044 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板5ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板6ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板7ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板8ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>细胞培养板9ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>样品7-ID</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>样品2-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>样品1-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>样品5-ID</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>样品3-ID</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>空白对照</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>样品9-ID</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>样品11-ID</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>样品4-ID</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>样品6-ID</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>样品10-ID</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>样品8-ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>